--- a/Data/QDArchive_Final_Report.xlsx
+++ b/Data/QDArchive_Final_Report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,32 +436,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>repo_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>source_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>repository_url</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>file_url</t>
+          <t>endpoint_url</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_code</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>usability_note</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>timestamp</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>local_path</t>
         </is>
       </c>
     </row>
@@ -469,34 +469,32 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Zenodo Sample</t>
-        </is>
+      <c r="B2" t="n">
+        <v>7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://zenodo.org/</t>
+          <t>ADA (Australian Data Archive)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://zenodo.org/record/10058814/files/Qualitative_Data_Example.pdf?download=1</t>
+          <t>https://ada.edu.au/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Failed (404)</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-01 18:46</t>
+          <t>Accessible. Operational for automated probing.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-03-11 14:04</t>
         </is>
       </c>
     </row>
@@ -504,69 +502,32 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>UCL Archive</t>
-        </is>
+      <c r="B3" t="n">
+        <v>16</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://discovery.ucl.ac.uk/</t>
+          <t>Open Data LSA (Uni-Halle)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://discovery.ucl.ac.uk/id/eprint/1474246/1/Qualitative_Methodology_Appendix.pdf</t>
+          <t>https://opendata.uni-halle.de/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Connection Error</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-01 18:46</t>
+          <t>Accessible. Operational for automated probing.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Public Repo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://raw.githubusercontent.com/allisonhorst/palmerpenguins/main/README.md</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Success</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-03-01 18:46</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>C:\Users\Pc_Momeni\OneDrive\Documents\Seeding-QDArchive\Data\README.md</t>
+          <t>2026-03-11 14:04</t>
         </is>
       </c>
     </row>
